--- a/docs/Mapping_casi_uso/trascrizioni/Trascr_029.xlsx
+++ b/docs/Mapping_casi_uso/trascrizioni/Trascr_029.xlsx
@@ -47,7 +47,7 @@
     <t/>
   </si>
   <si>
-    <t>Allegato aggiuntivo</t>
+    <t>Allegato generico</t>
   </si>
   <si>
     <t>Formula</t>

--- a/docs/Mapping_casi_uso/trascrizioni/Trascr_029.xlsx
+++ b/docs/Mapping_casi_uso/trascrizioni/Trascr_029.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1155" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1624" uniqueCount="152">
   <si>
     <t>Sezione</t>
   </si>
@@ -323,27 +323,36 @@
     <t>nomeComuneAIRE</t>
   </si>
   <si>
+    <t>Genitore</t>
+  </si>
+  <si>
+    <t>evento.madre</t>
+  </si>
+  <si>
+    <t>evento.flagOmogenitoriale,=,false</t>
+  </si>
+  <si>
+    <t>flag firmatario</t>
+  </si>
+  <si>
+    <t>Trasmissione residenza estera</t>
+  </si>
+  <si>
+    <t>flagTrasmissioneResidenzaEstera</t>
+  </si>
+  <si>
     <t>Madre</t>
   </si>
   <si>
-    <t>evento.madre</t>
-  </si>
-  <si>
-    <t>flag firmatario</t>
-  </si>
-  <si>
-    <t>Trasmissione residenza estera</t>
-  </si>
-  <si>
-    <t>flagTrasmissioneResidenzaEstera</t>
+    <t>evento.flagOmogenitoriale,=,true</t>
+  </si>
+  <si>
+    <t>evento.padre</t>
   </si>
   <si>
     <t>Padre</t>
   </si>
   <si>
-    <t>evento.padre</t>
-  </si>
-  <si>
     <t>Autorità Mittente</t>
   </si>
   <si>
@@ -453,6 +462,12 @@
   </si>
   <si>
     <t>idTipoRichiedente</t>
+  </si>
+  <si>
+    <t>Adozione omogenitoriale</t>
+  </si>
+  <si>
+    <t>flagOmogenitoriale</t>
   </si>
 </sst>
 </file>
@@ -511,7 +526,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H165"/>
+  <dimension ref="A1:H232"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="19.171875" customWidth="true" bestFit="true"/>
@@ -1578,7 +1593,7 @@
         <v>10</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>20</v>
+        <v>105</v>
       </c>
     </row>
     <row r="47">
@@ -1601,7 +1616,7 @@
         <v>10</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>20</v>
+        <v>105</v>
       </c>
     </row>
     <row r="48">
@@ -1624,7 +1639,7 @@
         <v>10</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>20</v>
+        <v>105</v>
       </c>
     </row>
     <row r="49">
@@ -1647,7 +1662,7 @@
         <v>10</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>20</v>
+        <v>105</v>
       </c>
     </row>
     <row r="50">
@@ -1670,7 +1685,7 @@
         <v>10</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>20</v>
+        <v>105</v>
       </c>
     </row>
     <row r="51">
@@ -1693,7 +1708,7 @@
         <v>10</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>20</v>
+        <v>105</v>
       </c>
     </row>
     <row r="52">
@@ -1716,7 +1731,7 @@
         <v>10</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>20</v>
+        <v>105</v>
       </c>
     </row>
     <row r="53">
@@ -1739,7 +1754,7 @@
         <v>10</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>20</v>
+        <v>105</v>
       </c>
     </row>
     <row r="54">
@@ -1762,7 +1777,7 @@
         <v>10</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>20</v>
+        <v>105</v>
       </c>
     </row>
     <row r="55">
@@ -1785,7 +1800,7 @@
         <v>10</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>20</v>
+        <v>105</v>
       </c>
     </row>
     <row r="56">
@@ -1808,7 +1823,7 @@
         <v>10</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>20</v>
+        <v>105</v>
       </c>
     </row>
     <row r="57">
@@ -1831,7 +1846,7 @@
         <v>10</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>20</v>
+        <v>105</v>
       </c>
     </row>
     <row r="58">
@@ -1854,7 +1869,7 @@
         <v>10</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>20</v>
+        <v>105</v>
       </c>
     </row>
     <row r="59">
@@ -1877,7 +1892,7 @@
         <v>10</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>20</v>
+        <v>105</v>
       </c>
     </row>
     <row r="60">
@@ -1900,7 +1915,7 @@
         <v>10</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>20</v>
+        <v>105</v>
       </c>
     </row>
     <row r="61">
@@ -1923,7 +1938,7 @@
         <v>10</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>20</v>
+        <v>105</v>
       </c>
     </row>
     <row r="62">
@@ -1946,7 +1961,7 @@
         <v>10</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>20</v>
+        <v>105</v>
       </c>
     </row>
     <row r="63">
@@ -1969,7 +1984,7 @@
         <v>10</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>20</v>
+        <v>105</v>
       </c>
     </row>
     <row r="64">
@@ -1992,7 +2007,7 @@
         <v>10</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>20</v>
+        <v>105</v>
       </c>
     </row>
     <row r="65">
@@ -2015,7 +2030,7 @@
         <v>10</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>20</v>
+        <v>105</v>
       </c>
     </row>
     <row r="66">
@@ -2038,7 +2053,7 @@
         <v>10</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>20</v>
+        <v>105</v>
       </c>
     </row>
     <row r="67">
@@ -2061,7 +2076,7 @@
         <v>10</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>20</v>
+        <v>105</v>
       </c>
     </row>
     <row r="68">
@@ -2084,7 +2099,7 @@
         <v>10</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>20</v>
+        <v>105</v>
       </c>
     </row>
     <row r="69">
@@ -2107,7 +2122,7 @@
         <v>10</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>20</v>
+        <v>105</v>
       </c>
     </row>
     <row r="70">
@@ -2130,7 +2145,7 @@
         <v>10</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>20</v>
+        <v>105</v>
       </c>
     </row>
     <row r="71">
@@ -2153,7 +2168,7 @@
         <v>10</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>20</v>
+        <v>105</v>
       </c>
     </row>
     <row r="72">
@@ -2176,7 +2191,7 @@
         <v>10</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>20</v>
+        <v>105</v>
       </c>
     </row>
     <row r="73">
@@ -2184,7 +2199,7 @@
         <v>103</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>14</v>
@@ -2199,7 +2214,7 @@
         <v>10</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>20</v>
+        <v>105</v>
       </c>
     </row>
     <row r="74">
@@ -2222,7 +2237,7 @@
         <v>10</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>20</v>
+        <v>105</v>
       </c>
     </row>
     <row r="75">
@@ -2245,7 +2260,7 @@
         <v>10</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>20</v>
+        <v>105</v>
       </c>
     </row>
     <row r="76">
@@ -2268,7 +2283,7 @@
         <v>10</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>20</v>
+        <v>105</v>
       </c>
     </row>
     <row r="77">
@@ -2291,7 +2306,7 @@
         <v>10</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>20</v>
+        <v>105</v>
       </c>
     </row>
     <row r="78">
@@ -2299,7 +2314,7 @@
         <v>103</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>9</v>
@@ -2308,18 +2323,18 @@
         <v>104</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F78" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>20</v>
+        <v>105</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B79" s="2" t="s">
         <v>38</v>
@@ -2328,7 +2343,7 @@
         <v>9</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="E79" s="2" t="s">
         <v>40</v>
@@ -2337,12 +2352,12 @@
         <v>10</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>20</v>
+        <v>110</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B80" s="2" t="s">
         <v>41</v>
@@ -2351,7 +2366,7 @@
         <v>14</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="E80" s="2" t="s">
         <v>42</v>
@@ -2360,12 +2375,12 @@
         <v>10</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>20</v>
+        <v>110</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>43</v>
@@ -2374,7 +2389,7 @@
         <v>9</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="E81" s="2" t="s">
         <v>44</v>
@@ -2383,12 +2398,12 @@
         <v>10</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>20</v>
+        <v>110</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B82" s="2" t="s">
         <v>45</v>
@@ -2397,7 +2412,7 @@
         <v>14</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="E82" s="2" t="s">
         <v>46</v>
@@ -2406,12 +2421,12 @@
         <v>10</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>20</v>
+        <v>110</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B83" s="2" t="s">
         <v>47</v>
@@ -2420,7 +2435,7 @@
         <v>9</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="E83" s="2" t="s">
         <v>48</v>
@@ -2429,12 +2444,12 @@
         <v>10</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>20</v>
+        <v>110</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B84" s="2" t="s">
         <v>49</v>
@@ -2443,7 +2458,7 @@
         <v>9</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="E84" s="2" t="s">
         <v>50</v>
@@ -2452,12 +2467,12 @@
         <v>10</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>20</v>
+        <v>110</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B85" s="2" t="s">
         <v>51</v>
@@ -2466,7 +2481,7 @@
         <v>14</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="E85" s="2" t="s">
         <v>52</v>
@@ -2475,12 +2490,12 @@
         <v>10</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>20</v>
+        <v>110</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B86" s="2" t="s">
         <v>53</v>
@@ -2489,7 +2504,7 @@
         <v>14</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="E86" s="2" t="s">
         <v>54</v>
@@ -2498,12 +2513,12 @@
         <v>10</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>20</v>
+        <v>110</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B87" s="2" t="s">
         <v>55</v>
@@ -2512,7 +2527,7 @@
         <v>14</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="E87" s="2" t="s">
         <v>56</v>
@@ -2521,12 +2536,12 @@
         <v>10</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>20</v>
+        <v>110</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B88" s="2" t="s">
         <v>57</v>
@@ -2535,7 +2550,7 @@
         <v>9</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="E88" s="2" t="s">
         <v>58</v>
@@ -2544,12 +2559,12 @@
         <v>10</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>20</v>
+        <v>110</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B89" s="2" t="s">
         <v>59</v>
@@ -2558,7 +2573,7 @@
         <v>9</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="E89" s="2" t="s">
         <v>60</v>
@@ -2567,12 +2582,12 @@
         <v>10</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>20</v>
+        <v>110</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B90" s="2" t="s">
         <v>61</v>
@@ -2581,7 +2596,7 @@
         <v>9</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="E90" s="2" t="s">
         <v>62</v>
@@ -2590,12 +2605,12 @@
         <v>10</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>20</v>
+        <v>110</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B91" s="2" t="s">
         <v>63</v>
@@ -2604,7 +2619,7 @@
         <v>9</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="E91" s="2" t="s">
         <v>64</v>
@@ -2613,12 +2628,12 @@
         <v>10</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>20</v>
+        <v>110</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B92" s="2" t="s">
         <v>65</v>
@@ -2627,7 +2642,7 @@
         <v>9</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="E92" s="2" t="s">
         <v>66</v>
@@ -2636,12 +2651,12 @@
         <v>10</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>20</v>
+        <v>110</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B93" s="2" t="s">
         <v>67</v>
@@ -2650,7 +2665,7 @@
         <v>14</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="E93" s="2" t="s">
         <v>68</v>
@@ -2659,12 +2674,12 @@
         <v>10</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>20</v>
+        <v>110</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B94" s="2" t="s">
         <v>69</v>
@@ -2673,7 +2688,7 @@
         <v>14</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="E94" s="2" t="s">
         <v>70</v>
@@ -2682,12 +2697,12 @@
         <v>10</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>20</v>
+        <v>110</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B95" s="2" t="s">
         <v>71</v>
@@ -2696,7 +2711,7 @@
         <v>9</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="E95" s="2" t="s">
         <v>72</v>
@@ -2705,12 +2720,12 @@
         <v>10</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>20</v>
+        <v>110</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B96" s="2" t="s">
         <v>73</v>
@@ -2719,7 +2734,7 @@
         <v>9</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="E96" s="2" t="s">
         <v>74</v>
@@ -2728,12 +2743,12 @@
         <v>10</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>20</v>
+        <v>110</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B97" s="2" t="s">
         <v>75</v>
@@ -2742,7 +2757,7 @@
         <v>9</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="E97" s="2" t="s">
         <v>76</v>
@@ -2751,12 +2766,12 @@
         <v>10</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>20</v>
+        <v>110</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B98" s="2" t="s">
         <v>77</v>
@@ -2765,7 +2780,7 @@
         <v>9</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="E98" s="2" t="s">
         <v>78</v>
@@ -2774,12 +2789,12 @@
         <v>10</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>20</v>
+        <v>110</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B99" s="2" t="s">
         <v>79</v>
@@ -2788,7 +2803,7 @@
         <v>9</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="E99" s="2" t="s">
         <v>80</v>
@@ -2797,12 +2812,12 @@
         <v>10</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>20</v>
+        <v>110</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B100" s="2" t="s">
         <v>81</v>
@@ -2811,7 +2826,7 @@
         <v>9</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="E100" s="2" t="s">
         <v>82</v>
@@ -2820,12 +2835,12 @@
         <v>10</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>20</v>
+        <v>110</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B101" s="2" t="s">
         <v>83</v>
@@ -2834,7 +2849,7 @@
         <v>9</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="E101" s="2" t="s">
         <v>84</v>
@@ -2843,12 +2858,12 @@
         <v>10</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>20</v>
+        <v>110</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B102" s="2" t="s">
         <v>85</v>
@@ -2857,7 +2872,7 @@
         <v>9</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="E102" s="2" t="s">
         <v>86</v>
@@ -2866,12 +2881,12 @@
         <v>10</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>20</v>
+        <v>110</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B103" s="2" t="s">
         <v>87</v>
@@ -2880,7 +2895,7 @@
         <v>9</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="E103" s="2" t="s">
         <v>88</v>
@@ -2889,12 +2904,12 @@
         <v>10</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>20</v>
+        <v>110</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B104" s="2" t="s">
         <v>89</v>
@@ -2903,7 +2918,7 @@
         <v>14</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="E104" s="2" t="s">
         <v>90</v>
@@ -2912,12 +2927,12 @@
         <v>10</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>20</v>
+        <v>110</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B105" s="2" t="s">
         <v>91</v>
@@ -2926,7 +2941,7 @@
         <v>14</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="E105" s="2" t="s">
         <v>92</v>
@@ -2935,21 +2950,21 @@
         <v>10</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>20</v>
+        <v>110</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C106" s="2" t="s">
         <v>14</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="E106" s="2" t="s">
         <v>94</v>
@@ -2958,12 +2973,12 @@
         <v>10</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>20</v>
+        <v>110</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B107" s="2" t="s">
         <v>95</v>
@@ -2972,7 +2987,7 @@
         <v>9</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="E107" s="2" t="s">
         <v>96</v>
@@ -2981,12 +2996,12 @@
         <v>10</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>20</v>
+        <v>110</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B108" s="2" t="s">
         <v>97</v>
@@ -2995,7 +3010,7 @@
         <v>9</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="E108" s="2" t="s">
         <v>98</v>
@@ -3004,12 +3019,12 @@
         <v>10</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>20</v>
+        <v>110</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B109" s="2" t="s">
         <v>99</v>
@@ -3018,7 +3033,7 @@
         <v>9</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="E109" s="2" t="s">
         <v>100</v>
@@ -3027,12 +3042,12 @@
         <v>10</v>
       </c>
       <c r="G109" s="2" t="s">
-        <v>20</v>
+        <v>110</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B110" s="2" t="s">
         <v>101</v>
@@ -3041,7 +3056,7 @@
         <v>9</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="E110" s="2" t="s">
         <v>102</v>
@@ -3050,1271 +3065,2812 @@
         <v>10</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>20</v>
+        <v>110</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B111" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C111" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D111" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E111" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="B111" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="C111" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D111" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="E111" s="2" t="s">
-        <v>107</v>
-      </c>
       <c r="F111" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G111" s="2" t="s">
-        <v>20</v>
+        <v>110</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>111</v>
+        <v>38</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>113</v>
+        <v>40</v>
       </c>
       <c r="F112" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>20</v>
+        <v>105</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>114</v>
+        <v>41</v>
       </c>
       <c r="C113" s="2" t="s">
         <v>14</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>115</v>
+        <v>42</v>
       </c>
       <c r="F113" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G113" s="2" t="s">
-        <v>20</v>
+        <v>105</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>116</v>
+        <v>43</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>117</v>
+        <v>44</v>
       </c>
       <c r="F114" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>20</v>
+        <v>105</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>118</v>
+        <v>45</v>
       </c>
       <c r="C115" s="2" t="s">
         <v>14</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E115" s="2" t="s">
-        <v>119</v>
+        <v>46</v>
       </c>
       <c r="F115" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>20</v>
+        <v>105</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>120</v>
+        <v>47</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>121</v>
+        <v>48</v>
       </c>
       <c r="F116" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>20</v>
+        <v>105</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>122</v>
+        <v>49</v>
       </c>
       <c r="C117" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>123</v>
+        <v>50</v>
       </c>
       <c r="F117" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G117" s="2" t="s">
-        <v>20</v>
+        <v>105</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>124</v>
+        <v>51</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>125</v>
+        <v>52</v>
       </c>
       <c r="F118" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G118" s="2" t="s">
-        <v>20</v>
+        <v>105</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>126</v>
+        <v>53</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>127</v>
+        <v>54</v>
       </c>
       <c r="F119" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G119" s="2" t="s">
-        <v>20</v>
+        <v>105</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>128</v>
+        <v>55</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>129</v>
+        <v>56</v>
       </c>
       <c r="F120" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G120" s="2" t="s">
-        <v>20</v>
+        <v>105</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="C121" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>130</v>
+        <v>58</v>
       </c>
       <c r="F121" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G121" s="2" t="s">
-        <v>20</v>
+        <v>105</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="s">
-        <v>131</v>
+        <v>103</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="C122" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>132</v>
+        <v>111</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="F122" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G122" s="2" t="s">
-        <v>133</v>
+        <v>105</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="s">
-        <v>131</v>
+        <v>103</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>132</v>
+        <v>111</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="F123" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G123" s="2" t="s">
-        <v>133</v>
+        <v>105</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="s">
-        <v>131</v>
+        <v>103</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="C124" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>132</v>
+        <v>111</v>
       </c>
       <c r="E124" s="2" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="F124" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G124" s="2" t="s">
-        <v>133</v>
+        <v>105</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="s">
-        <v>131</v>
+        <v>103</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="C125" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>132</v>
+        <v>111</v>
       </c>
       <c r="E125" s="2" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="F125" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G125" s="2" t="s">
-        <v>133</v>
+        <v>105</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="s">
-        <v>131</v>
+        <v>103</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>132</v>
+        <v>111</v>
       </c>
       <c r="E126" s="2" t="s">
-        <v>48</v>
+        <v>68</v>
       </c>
       <c r="F126" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G126" s="2" t="s">
-        <v>133</v>
+        <v>105</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="s">
-        <v>131</v>
+        <v>103</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>132</v>
+        <v>111</v>
       </c>
       <c r="E127" s="2" t="s">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="F127" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G127" s="2" t="s">
-        <v>133</v>
+        <v>105</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="s">
-        <v>131</v>
+        <v>103</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="C128" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>132</v>
+        <v>111</v>
       </c>
       <c r="E128" s="2" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="F128" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G128" s="2" t="s">
-        <v>133</v>
+        <v>105</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="s">
-        <v>131</v>
+        <v>103</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="C129" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>132</v>
+        <v>111</v>
       </c>
       <c r="E129" s="2" t="s">
-        <v>54</v>
+        <v>74</v>
       </c>
       <c r="F129" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G129" s="2" t="s">
-        <v>133</v>
+        <v>105</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="s">
-        <v>131</v>
+        <v>103</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="C130" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>132</v>
+        <v>111</v>
       </c>
       <c r="E130" s="2" t="s">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="F130" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G130" s="2" t="s">
-        <v>133</v>
+        <v>105</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="s">
-        <v>131</v>
+        <v>103</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>57</v>
+        <v>77</v>
       </c>
       <c r="C131" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>132</v>
+        <v>111</v>
       </c>
       <c r="E131" s="2" t="s">
-        <v>58</v>
+        <v>78</v>
       </c>
       <c r="F131" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G131" s="2" t="s">
-        <v>133</v>
+        <v>105</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="s">
-        <v>131</v>
+        <v>103</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>59</v>
+        <v>79</v>
       </c>
       <c r="C132" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>132</v>
+        <v>111</v>
       </c>
       <c r="E132" s="2" t="s">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="F132" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G132" s="2" t="s">
-        <v>133</v>
+        <v>105</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="s">
-        <v>131</v>
+        <v>103</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>61</v>
+        <v>81</v>
       </c>
       <c r="C133" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>132</v>
+        <v>111</v>
       </c>
       <c r="E133" s="2" t="s">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c r="F133" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G133" s="2" t="s">
-        <v>133</v>
+        <v>105</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="s">
-        <v>131</v>
+        <v>103</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>63</v>
+        <v>83</v>
       </c>
       <c r="C134" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>132</v>
+        <v>111</v>
       </c>
       <c r="E134" s="2" t="s">
-        <v>64</v>
+        <v>84</v>
       </c>
       <c r="F134" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G134" s="2" t="s">
-        <v>133</v>
+        <v>105</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="s">
-        <v>131</v>
+        <v>103</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="C135" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>132</v>
+        <v>111</v>
       </c>
       <c r="E135" s="2" t="s">
-        <v>66</v>
+        <v>86</v>
       </c>
       <c r="F135" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G135" s="2" t="s">
-        <v>133</v>
+        <v>105</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="s">
-        <v>131</v>
+        <v>103</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>67</v>
+        <v>87</v>
       </c>
       <c r="C136" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>132</v>
+        <v>111</v>
       </c>
       <c r="E136" s="2" t="s">
-        <v>68</v>
+        <v>88</v>
       </c>
       <c r="F136" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G136" s="2" t="s">
-        <v>133</v>
+        <v>105</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="s">
-        <v>131</v>
+        <v>103</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>69</v>
+        <v>89</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>132</v>
+        <v>111</v>
       </c>
       <c r="E137" s="2" t="s">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="F137" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G137" s="2" t="s">
-        <v>133</v>
+        <v>105</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="s">
-        <v>131</v>
+        <v>103</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>71</v>
+        <v>91</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>132</v>
+        <v>111</v>
       </c>
       <c r="E138" s="2" t="s">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="F138" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G138" s="2" t="s">
-        <v>133</v>
+        <v>105</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="s">
-        <v>131</v>
+        <v>103</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>73</v>
+        <v>106</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>132</v>
+        <v>111</v>
       </c>
       <c r="E139" s="2" t="s">
-        <v>74</v>
+        <v>94</v>
       </c>
       <c r="F139" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G139" s="2" t="s">
-        <v>133</v>
+        <v>105</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="s">
-        <v>131</v>
+        <v>103</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="C140" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>132</v>
+        <v>111</v>
       </c>
       <c r="E140" s="2" t="s">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="F140" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G140" s="2" t="s">
-        <v>133</v>
+        <v>105</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="s">
-        <v>131</v>
+        <v>103</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="C141" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>132</v>
+        <v>111</v>
       </c>
       <c r="E141" s="2" t="s">
-        <v>78</v>
+        <v>98</v>
       </c>
       <c r="F141" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G141" s="2" t="s">
-        <v>133</v>
+        <v>105</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="s">
-        <v>131</v>
+        <v>103</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="C142" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>132</v>
+        <v>111</v>
       </c>
       <c r="E142" s="2" t="s">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="F142" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G142" s="2" t="s">
-        <v>133</v>
+        <v>105</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="s">
-        <v>131</v>
+        <v>103</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="C143" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>132</v>
+        <v>111</v>
       </c>
       <c r="E143" s="2" t="s">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="F143" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G143" s="2" t="s">
-        <v>133</v>
+        <v>105</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="s">
-        <v>131</v>
+        <v>103</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="C144" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>132</v>
+        <v>111</v>
       </c>
       <c r="E144" s="2" t="s">
-        <v>84</v>
+        <v>108</v>
       </c>
       <c r="F144" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G144" s="2" t="s">
-        <v>133</v>
+        <v>105</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="s">
-        <v>131</v>
+        <v>112</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>85</v>
+        <v>38</v>
       </c>
       <c r="C145" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>132</v>
+        <v>111</v>
       </c>
       <c r="E145" s="2" t="s">
-        <v>86</v>
+        <v>40</v>
       </c>
       <c r="F145" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G145" s="2" t="s">
-        <v>133</v>
+        <v>110</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="s">
-        <v>131</v>
+        <v>112</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>87</v>
+        <v>41</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>132</v>
+        <v>111</v>
       </c>
       <c r="E146" s="2" t="s">
-        <v>88</v>
+        <v>42</v>
       </c>
       <c r="F146" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G146" s="2" t="s">
-        <v>133</v>
+        <v>110</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="s">
-        <v>131</v>
+        <v>112</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>89</v>
+        <v>43</v>
       </c>
       <c r="C147" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>132</v>
+        <v>111</v>
       </c>
       <c r="E147" s="2" t="s">
-        <v>90</v>
+        <v>44</v>
       </c>
       <c r="F147" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G147" s="2" t="s">
-        <v>133</v>
+        <v>110</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="s">
-        <v>131</v>
+        <v>112</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>91</v>
+        <v>45</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>132</v>
+        <v>111</v>
       </c>
       <c r="E148" s="2" t="s">
-        <v>92</v>
+        <v>46</v>
       </c>
       <c r="F148" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G148" s="2" t="s">
-        <v>133</v>
+        <v>110</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="s">
-        <v>131</v>
+        <v>112</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>93</v>
+        <v>47</v>
       </c>
       <c r="C149" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>132</v>
+        <v>111</v>
       </c>
       <c r="E149" s="2" t="s">
-        <v>94</v>
+        <v>48</v>
       </c>
       <c r="F149" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G149" s="2" t="s">
-        <v>133</v>
+        <v>110</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="s">
-        <v>131</v>
+        <v>112</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>95</v>
+        <v>49</v>
       </c>
       <c r="C150" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>132</v>
+        <v>111</v>
       </c>
       <c r="E150" s="2" t="s">
-        <v>96</v>
+        <v>50</v>
       </c>
       <c r="F150" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G150" s="2" t="s">
-        <v>133</v>
+        <v>110</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="s">
-        <v>131</v>
+        <v>112</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>97</v>
+        <v>51</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>132</v>
+        <v>111</v>
       </c>
       <c r="E151" s="2" t="s">
-        <v>98</v>
+        <v>52</v>
       </c>
       <c r="F151" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G151" s="2" t="s">
-        <v>133</v>
+        <v>110</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="s">
-        <v>131</v>
+        <v>112</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>99</v>
+        <v>53</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D152" s="2" t="s">
-        <v>132</v>
+        <v>111</v>
       </c>
       <c r="E152" s="2" t="s">
-        <v>100</v>
+        <v>54</v>
       </c>
       <c r="F152" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G152" s="2" t="s">
-        <v>133</v>
+        <v>110</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="s">
-        <v>131</v>
+        <v>112</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>101</v>
+        <v>55</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D153" s="2" t="s">
-        <v>132</v>
+        <v>111</v>
       </c>
       <c r="E153" s="2" t="s">
-        <v>102</v>
+        <v>56</v>
       </c>
       <c r="F153" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G153" s="2" t="s">
-        <v>133</v>
+        <v>110</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="s">
-        <v>131</v>
+        <v>112</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>116</v>
+        <v>57</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>134</v>
+        <v>111</v>
       </c>
       <c r="E154" s="2" t="s">
-        <v>117</v>
+        <v>58</v>
       </c>
       <c r="F154" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G154" s="2" t="s">
-        <v>135</v>
+        <v>110</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="s">
-        <v>131</v>
+        <v>112</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>118</v>
+        <v>59</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D155" s="2" t="s">
-        <v>134</v>
+        <v>111</v>
       </c>
       <c r="E155" s="2" t="s">
-        <v>119</v>
+        <v>60</v>
       </c>
       <c r="F155" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G155" s="2" t="s">
-        <v>135</v>
+        <v>110</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="s">
-        <v>131</v>
+        <v>112</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>120</v>
+        <v>61</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D156" s="2" t="s">
-        <v>134</v>
+        <v>111</v>
       </c>
       <c r="E156" s="2" t="s">
-        <v>121</v>
+        <v>62</v>
       </c>
       <c r="F156" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G156" s="2" t="s">
-        <v>135</v>
+        <v>110</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="s">
-        <v>131</v>
+        <v>112</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>122</v>
+        <v>63</v>
       </c>
       <c r="C157" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D157" s="2" t="s">
-        <v>134</v>
+        <v>111</v>
       </c>
       <c r="E157" s="2" t="s">
-        <v>123</v>
+        <v>64</v>
       </c>
       <c r="F157" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G157" s="2" t="s">
-        <v>135</v>
+        <v>110</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="s">
-        <v>131</v>
+        <v>112</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>124</v>
+        <v>65</v>
       </c>
       <c r="C158" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D158" s="2" t="s">
-        <v>134</v>
+        <v>111</v>
       </c>
       <c r="E158" s="2" t="s">
-        <v>125</v>
+        <v>66</v>
       </c>
       <c r="F158" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G158" s="2" t="s">
-        <v>135</v>
+        <v>110</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="s">
-        <v>131</v>
+        <v>112</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>126</v>
+        <v>67</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D159" s="2" t="s">
-        <v>134</v>
+        <v>111</v>
       </c>
       <c r="E159" s="2" t="s">
-        <v>127</v>
+        <v>68</v>
       </c>
       <c r="F159" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G159" s="2" t="s">
-        <v>135</v>
+        <v>110</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="s">
-        <v>131</v>
+        <v>112</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>128</v>
+        <v>69</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D160" s="2" t="s">
-        <v>134</v>
+        <v>111</v>
       </c>
       <c r="E160" s="2" t="s">
-        <v>129</v>
+        <v>70</v>
       </c>
       <c r="F160" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G160" s="2" t="s">
-        <v>135</v>
+        <v>110</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="s">
-        <v>131</v>
+        <v>112</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>136</v>
+        <v>71</v>
       </c>
       <c r="C161" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D161" s="2" t="s">
-        <v>134</v>
+        <v>111</v>
       </c>
       <c r="E161" s="2" t="s">
-        <v>137</v>
+        <v>72</v>
       </c>
       <c r="F161" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G161" s="2" t="s">
-        <v>135</v>
+        <v>110</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="s">
-        <v>131</v>
+        <v>112</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>138</v>
+        <v>73</v>
       </c>
       <c r="C162" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D162" s="2" t="s">
-        <v>134</v>
+        <v>111</v>
       </c>
       <c r="E162" s="2" t="s">
-        <v>139</v>
+        <v>74</v>
       </c>
       <c r="F162" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G162" s="2" t="s">
-        <v>135</v>
+        <v>110</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="s">
-        <v>131</v>
+        <v>112</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>140</v>
+        <v>75</v>
       </c>
       <c r="C163" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D163" s="2" t="s">
-        <v>134</v>
+        <v>111</v>
       </c>
       <c r="E163" s="2" t="s">
-        <v>130</v>
+        <v>76</v>
       </c>
       <c r="F163" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G163" s="2" t="s">
-        <v>135</v>
+        <v>110</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="s">
-        <v>141</v>
+        <v>112</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>141</v>
+        <v>77</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D164" s="2" t="s">
-        <v>18</v>
+        <v>111</v>
       </c>
       <c r="E164" s="2" t="s">
-        <v>142</v>
+        <v>78</v>
       </c>
       <c r="F164" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G164" s="2" t="s">
-        <v>20</v>
+        <v>110</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="B165" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C165" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D165" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E165" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="F165" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G165" s="2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="B166" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C166" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D166" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E166" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="F166" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G166" s="2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="B167" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C167" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D167" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E167" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="F167" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G167" s="2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="B168" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C168" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D168" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E168" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="F168" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G168" s="2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="B169" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C169" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D169" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E169" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="F169" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G169" s="2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="B170" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C170" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D170" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E170" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="F170" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G170" s="2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="B171" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C171" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D171" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E171" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="F171" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G171" s="2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="B172" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C172" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D172" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E172" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="F172" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G172" s="2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="B173" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C173" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D173" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E173" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="F173" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G173" s="2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="B174" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C174" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D174" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E174" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="F174" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G174" s="2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="B175" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C175" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D175" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E175" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="F175" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G175" s="2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="B176" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C176" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D176" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E176" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="F176" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G176" s="2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="B177" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C177" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D177" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E177" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="F177" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G177" s="2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B178" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C178" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D178" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="E178" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="F178" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G178" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B179" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C179" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D179" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="E179" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="F179" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G179" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B180" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C180" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D180" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="E180" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="F180" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G180" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B181" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C181" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D181" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="E181" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="F181" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G181" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B182" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C182" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D182" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="E182" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="F182" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G182" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B183" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C183" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D183" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="E183" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="F183" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G183" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B184" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C184" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D184" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="E184" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="F184" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G184" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B185" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C185" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D185" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="E185" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="F185" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G185" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B186" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C186" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D186" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="E186" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="F186" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G186" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B187" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C187" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D187" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="E187" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="F187" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G187" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="B188" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C188" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D188" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="E188" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F188" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G188" s="2" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="B189" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C189" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D189" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="E189" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F189" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G189" s="2" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="B190" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C190" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D190" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="E190" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="F190" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G190" s="2" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="B191" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C191" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D191" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="E191" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F191" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G191" s="2" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="B192" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C192" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D192" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="E192" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="F192" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G192" s="2" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="B193" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C193" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D193" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="E193" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F193" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G193" s="2" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="B194" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C194" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D194" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="E194" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F194" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G194" s="2" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="B195" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C195" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D195" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="E195" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F195" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G195" s="2" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="B196" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C196" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D196" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="E196" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F196" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G196" s="2" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="B197" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C197" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D197" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="E197" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="F197" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G197" s="2" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="B198" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C198" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D198" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="E198" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="F198" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G198" s="2" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="B199" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C199" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D199" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="E199" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="F199" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G199" s="2" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="B200" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C200" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D200" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="E200" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="F200" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G200" s="2" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="B201" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C201" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D201" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="E201" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="F201" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G201" s="2" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="B202" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C202" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D202" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="E202" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="F202" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G202" s="2" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="B203" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C203" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D203" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="E203" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="F203" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G203" s="2" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="B204" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C204" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D204" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="E204" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="F204" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G204" s="2" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="B205" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C205" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D205" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="E205" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="F205" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G205" s="2" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="B206" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C206" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D206" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="E206" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="F206" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G206" s="2" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="B207" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C207" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D207" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="E207" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="F207" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G207" s="2" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="B208" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C208" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D208" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="E208" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="F208" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G208" s="2" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="B209" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C209" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D209" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="E209" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="F209" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G209" s="2" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="B210" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C210" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D210" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="E210" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="F210" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G210" s="2" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="B211" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C211" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D211" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="E211" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="F211" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G211" s="2" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="B212" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C212" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D212" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="E212" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="F212" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G212" s="2" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="B213" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C213" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D213" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="E213" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="F213" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G213" s="2" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="B214" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C214" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D214" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="E214" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="F214" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G214" s="2" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="B215" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C215" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D215" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="E215" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="F215" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G215" s="2" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="B216" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C216" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D216" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="E216" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="F216" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G216" s="2" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="B217" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C217" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D217" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="E217" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="F217" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G217" s="2" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="B218" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C218" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D218" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="E218" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="F218" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G218" s="2" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="B219" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C219" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D219" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="E219" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="F219" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G219" s="2" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="B220" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C220" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D220" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E220" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="F220" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G220" s="2" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="B221" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C221" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D221" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E221" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="F221" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G221" s="2" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="B222" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C222" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D222" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E222" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="F222" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G222" s="2" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="B223" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C223" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D223" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E223" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="F223" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G223" s="2" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="B224" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C224" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D224" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E224" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="F224" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G224" s="2" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="B225" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C225" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D225" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E225" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="F225" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G225" s="2" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="B226" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C226" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D226" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E226" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="F226" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G226" s="2" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="B227" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C227" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D227" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E227" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="F227" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G227" s="2" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="B228" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C228" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D228" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E228" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="F228" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G228" s="2" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="B229" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="B165" s="2" t="s">
+      <c r="C229" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D229" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E229" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="F229" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G229" s="2" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="C165" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D165" s="2" t="s">
+      <c r="B230" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C230" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D230" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E230" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="E165" s="2" t="s">
+      <c r="F230" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G230" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="F165" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G165" s="2" t="s">
+      <c r="B231" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="C231" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D231" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="E231" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="F231" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G231" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="B232" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="C232" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D232" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E232" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="F232" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G232" s="2" t="s">
         <v>20</v>
       </c>
     </row>
